--- a/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="必嘉坊．迎汇 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="必嘉坊．迎汇" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +237,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -13594,175 +13632,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>必嘉坊．迎汇 - 必嘉坊．迎汇 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>必嘉坊．迎汇 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>280 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>273 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 招标单位
@@ -13770,7 +13808,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 380呎 (2房)
 招标单位
@@ -13778,7 +13816,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 433呎 (2房)
 招标单位
@@ -13786,8 +13824,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $513万
@@ -13795,7 +13833,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $659万
@@ -13803,7 +13841,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 271呎 (1房)
 招标单位
@@ -13811,24 +13849,24 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>J | 400呎 (2房)
-$1,186万
+$1186万
 $29,639/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>K | 377呎 (1房)
-$1,021万
+$1021万
 $27,072/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $578万
@@ -13836,7 +13874,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 招标单位
@@ -13844,7 +13882,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 招标单位
@@ -13853,13 +13891,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $431万
@@ -13867,7 +13905,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $936万
@@ -13875,16 +13913,16 @@
 (23年-01月)</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 514呎 (3房)
-$1,126万
+$1126万
 $21,898/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $546万
@@ -13892,7 +13930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $598万
@@ -13900,7 +13938,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>G | 271呎 (1房)
 $549万
@@ -13908,16 +13946,16 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>J | 508呎 (3房)
-$1,049万
+$1049万
 $20,644/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $811万
@@ -13925,7 +13963,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $451万
@@ -13933,7 +13971,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $416万
@@ -13941,7 +13979,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $650万
@@ -13950,13 +13988,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $430万
@@ -13964,7 +14002,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $848万
@@ -13972,16 +14010,16 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 515呎 (3房)
-$1,209万
+$1209万
 $23,483/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $544万
@@ -13989,7 +14027,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $556万
@@ -13997,7 +14035,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 271呎 (1房)
 $590万
@@ -14005,16 +14043,16 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>J | 508呎 (3房)
-$1,125万
+$1125万
 $22,144/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $867万
@@ -14022,7 +14060,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $450万
@@ -14030,7 +14068,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $415万
@@ -14038,7 +14076,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $641万
@@ -14047,13 +14085,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $429万
@@ -14061,7 +14099,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $814万
@@ -14069,7 +14107,7 @@
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $589万
@@ -14077,7 +14115,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $552万
@@ -14085,7 +14123,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $585万
@@ -14093,7 +14131,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $554万
@@ -14101,7 +14139,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $600万
@@ -14109,7 +14147,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $538万
@@ -14117,7 +14155,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $558万
@@ -14125,7 +14163,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $787万
@@ -14133,7 +14171,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $418万
@@ -14141,7 +14179,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $414万
@@ -14149,7 +14187,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $617万
@@ -14158,13 +14196,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $427万
@@ -14172,7 +14210,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $812万
@@ -14180,7 +14218,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $588万
@@ -14188,7 +14226,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $550万
@@ -14196,7 +14234,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $541万
@@ -14204,7 +14242,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $592万
@@ -14212,7 +14250,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $583万
@@ -14220,7 +14258,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $536万
@@ -14228,7 +14266,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $556万
@@ -14236,7 +14274,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $784万
@@ -14244,7 +14282,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $416万
@@ -14252,7 +14290,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="M10" s="18" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $412万
@@ -14260,7 +14298,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N9" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $677万
@@ -14269,13 +14307,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $426万
@@ -14283,7 +14321,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $810万
@@ -14291,7 +14329,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $586万
@@ -14299,7 +14337,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $548万
@@ -14307,7 +14345,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $539万
@@ -14315,7 +14353,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $606万
@@ -14323,7 +14361,7 @@
 (23年-08月)</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $542万
@@ -14331,7 +14369,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $573万
@@ -14339,7 +14377,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $532万
@@ -14347,7 +14385,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $791万
@@ -14355,7 +14393,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $415万
@@ -14363,7 +14401,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $411万
@@ -14371,7 +14409,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $613万
@@ -14380,13 +14418,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $425万
@@ -14394,7 +14432,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $807万
@@ -14402,7 +14440,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $584万
@@ -14410,7 +14448,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $589万
@@ -14418,7 +14456,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $544万
@@ -14426,7 +14464,7 @@
 (23年-05月)</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $592万
@@ -14434,7 +14472,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $541万
@@ -14442,7 +14480,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $533万
@@ -14450,7 +14488,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $553万
@@ -14458,7 +14496,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $780万
@@ -14466,7 +14504,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $427万
@@ -14474,7 +14512,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M12" s="18" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $410万
@@ -14482,7 +14520,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="N11" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $654万
@@ -14491,13 +14529,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $424万
@@ -14505,7 +14543,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $805万
@@ -14513,7 +14551,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $656万
@@ -14521,7 +14559,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $585万
@@ -14529,7 +14567,7 @@
 (23年-05月)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $575万
@@ -14537,7 +14575,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $587万
@@ -14545,7 +14583,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $539万
@@ -14553,7 +14591,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $532万
@@ -14561,7 +14599,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $591万
@@ -14569,7 +14607,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $834万
@@ -14577,7 +14615,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $426万
@@ -14585,7 +14623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $414万
@@ -14593,7 +14631,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="N12" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $613万
@@ -14602,13 +14640,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $423万
@@ -14616,7 +14654,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $803万
@@ -14624,7 +14662,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $579万
@@ -14632,7 +14670,7 @@
 (23年-08月)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $562万
@@ -14640,7 +14678,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $540万
@@ -14648,7 +14686,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $546万
@@ -14656,7 +14694,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $537万
@@ -14664,7 +14702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $568万
@@ -14672,7 +14710,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $592万
@@ -14680,7 +14718,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $775万
@@ -14688,7 +14726,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $455万
@@ -14696,7 +14734,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $446万
@@ -14704,7 +14742,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="N13" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $648万
@@ -14713,13 +14751,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $421万
@@ -14727,7 +14765,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $798万
@@ -14735,7 +14773,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $652万
@@ -14743,7 +14781,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $542万
@@ -14751,7 +14789,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $533万
@@ -14759,7 +14797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $584万
@@ -14767,7 +14805,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $542万
@@ -14775,7 +14813,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $570万
@@ -14783,7 +14821,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $587万
@@ -14791,7 +14829,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $849万
@@ -14799,7 +14837,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $428万
@@ -14807,7 +14845,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $395万
@@ -14815,7 +14853,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N14" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $646万
@@ -14824,13 +14862,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $420万
@@ -14838,7 +14876,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $811万
@@ -14846,7 +14884,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $650万
@@ -14854,7 +14892,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $540万
@@ -14862,7 +14900,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $570万
@@ -14870,7 +14908,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $543万
@@ -14878,7 +14916,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $534万
@@ -14886,7 +14924,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $527万
@@ -14894,7 +14932,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $546万
@@ -14902,7 +14940,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $789万
@@ -14910,7 +14948,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $464万
@@ -14918,7 +14956,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M16" s="18" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $394万
@@ -14926,7 +14964,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $648万
@@ -14935,13 +14973,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $471万
@@ -14949,7 +14987,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $793万
@@ -14957,7 +14995,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $574万
@@ -14965,7 +15003,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $539万
@@ -14973,7 +15011,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $571万
@@ -14981,7 +15019,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $541万
@@ -14989,7 +15027,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $571万
@@ -14997,7 +15035,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $563万
@@ -15005,7 +15043,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $587万
@@ -15013,7 +15051,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $782万
@@ -15021,7 +15059,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="18" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $421万
@@ -15029,7 +15067,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="M17" s="18" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $393万
@@ -15037,7 +15075,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N17" s="18" t="inlineStr">
+      <c r="N16" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $599万
@@ -15046,13 +15084,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $470万
@@ -15060,7 +15098,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $791万
@@ -15068,7 +15106,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $572万
@@ -15076,7 +15114,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $537万
@@ -15084,7 +15122,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $546万
@@ -15092,7 +15130,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $540万
@@ -15100,7 +15138,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $531万
@@ -15108,7 +15146,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $565万
@@ -15116,7 +15154,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $585万
@@ -15124,7 +15162,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $761万
@@ -15132,7 +15170,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $423万
@@ -15140,7 +15178,7 @@
 (23年-03月)</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $409万
@@ -15148,7 +15186,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="N18" s="18" t="inlineStr">
+      <c r="N17" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $597万
@@ -15157,13 +15195,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $468万
@@ -15171,7 +15209,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $818万
@@ -15179,7 +15217,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $571万
@@ -15187,7 +15225,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $536万
@@ -15195,7 +15233,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $565万
@@ -15203,7 +15241,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $538万
@@ -15211,7 +15249,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $568万
@@ -15219,7 +15257,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $560万
@@ -15227,7 +15265,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="18" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $541万
@@ -15235,7 +15273,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="18" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $770万
@@ -15243,7 +15281,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L19" s="18" t="inlineStr">
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $445万
@@ -15251,7 +15289,7 @@
 (23年-05月)</t>
         </is>
       </c>
-      <c r="M19" s="18" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $391万
@@ -15259,7 +15297,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N19" s="18" t="inlineStr">
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $642万
@@ -15268,13 +15306,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $467万
@@ -15282,7 +15320,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $758万
@@ -15290,7 +15328,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $569万
@@ -15298,7 +15336,7 @@
 (23年-09月)</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $534万
@@ -15306,7 +15344,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $525万
@@ -15314,7 +15352,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $575万
@@ -15322,7 +15360,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $528万
@@ -15330,7 +15368,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $538万
@@ -15338,7 +15376,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $540万
@@ -15346,7 +15384,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $741万
@@ -15354,7 +15392,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="18" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $412万
@@ -15362,7 +15400,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M20" s="18" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $438万
@@ -15370,7 +15408,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="N20" s="18" t="inlineStr">
+      <c r="N19" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $600万
@@ -15379,13 +15417,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $466万
@@ -15393,7 +15431,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $784万
@@ -15401,7 +15439,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $588万
@@ -15409,7 +15447,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $533万
@@ -15417,7 +15455,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $541万
@@ -15425,7 +15463,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $535万
@@ -15433,7 +15471,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $564万
@@ -15441,7 +15479,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $519万
@@ -15449,7 +15487,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $577万
@@ -15457,7 +15495,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $792万
@@ -15465,7 +15503,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $411万
@@ -15473,7 +15511,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M21" s="18" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $388万
@@ -15481,7 +15519,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N21" s="18" t="inlineStr">
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $612万
@@ -15490,13 +15528,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $418万
@@ -15504,7 +15542,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $814万
@@ -15512,7 +15550,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $566万
@@ -15520,7 +15558,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $531万
@@ -15528,7 +15566,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $574万
@@ -15536,7 +15574,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $571万
@@ -15544,7 +15582,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $563万
@@ -15552,7 +15590,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $518万
@@ -15560,7 +15598,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $575万
@@ -15568,7 +15606,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $766万
@@ -15576,7 +15614,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="18" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $438万
@@ -15584,7 +15622,7 @@
 (23年-03月)</t>
         </is>
       </c>
-      <c r="M22" s="18" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $387万
@@ -15592,7 +15630,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="N22" s="18" t="inlineStr">
+      <c r="N21" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $631万
@@ -15601,13 +15639,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $412万
@@ -15615,7 +15653,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $746万
@@ -15623,7 +15661,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $583万
@@ -15631,7 +15669,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $568万
@@ -15639,7 +15677,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $558万
@@ -15647,7 +15685,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $531万
@@ -15655,7 +15693,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $541万
@@ -15663,7 +15701,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="18" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $553万
@@ -15671,7 +15709,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="18" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $577万
@@ -15679,7 +15717,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="18" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $745万
@@ -15687,7 +15725,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="18" t="inlineStr">
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $436万
@@ -15695,7 +15733,7 @@
 (23年-03月)</t>
         </is>
       </c>
-      <c r="M23" s="18" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $434万
@@ -15703,7 +15741,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="N23" s="18" t="inlineStr">
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $585万
@@ -15712,13 +15750,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 223呎 (开放式)
 $412万
@@ -15726,7 +15764,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $714万
@@ -15734,7 +15772,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $591万
@@ -15742,7 +15780,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 273呎 (1房)
 $568万
@@ -15750,7 +15788,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $538万
@@ -15758,7 +15796,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $531万
@@ -15766,7 +15804,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $523万
@@ -15774,7 +15812,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $562万
@@ -15782,7 +15820,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $577万
@@ -15790,7 +15828,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $745万
@@ -15798,7 +15836,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $406万
@@ -15806,7 +15844,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M24" s="18" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $394万
@@ -15814,7 +15852,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="N24" s="18" t="inlineStr">
+      <c r="N23" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $590万
@@ -15823,13 +15861,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $461万
@@ -15837,7 +15875,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $777万
@@ -15845,7 +15883,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $562万
@@ -15853,7 +15891,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $528万
@@ -15861,7 +15899,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $556万
@@ -15869,7 +15907,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $547万
@@ -15877,7 +15915,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $522万
@@ -15885,7 +15923,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $552万
@@ -15893,7 +15931,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="18" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $533万
@@ -15901,7 +15939,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="18" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $767万
@@ -15909,7 +15947,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L25" s="18" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $433万
@@ -15917,7 +15955,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M25" s="18" t="inlineStr">
+      <c r="M24" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $464万
@@ -15925,7 +15963,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="N25" s="18" t="inlineStr">
+      <c r="N24" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $581万
@@ -15934,13 +15972,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 222呎 (开放式)
 $500万
@@ -15948,7 +15986,7 @@
 (22年-11月)</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 378呎 (2房)
 $772万
@@ -15956,7 +15994,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 278呎 (1房)
 $560万
@@ -15964,7 +16002,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 274呎 (1房)
 $564万
@@ -15972,7 +16010,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 270呎 (1房)
 $554万
@@ -15980,7 +16018,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $528万
@@ -15988,7 +16026,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $520万
@@ -15996,7 +16034,7 @@
 (23年-04月)</t>
         </is>
       </c>
-      <c r="I26" s="18" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 270呎 (1房)
 $513万
@@ -16004,7 +16042,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="18" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>J | 276呎 (1房)
 $532万
@@ -16012,7 +16050,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="K26" s="18" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>K | 374呎 (1房)
 $739万
@@ -16020,7 +16058,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L26" s="18" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>L | 214呎 (开放式)
 $400万
@@ -16028,7 +16066,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M26" s="18" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $399万
@@ -16036,7 +16074,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="N26" s="18" t="inlineStr">
+      <c r="N25" s="22" t="inlineStr">
         <is>
           <t>N | 324呎 (1房)
 $580万
@@ -16045,13 +16083,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 201呎 (开放式)
 $408万
@@ -16059,7 +16097,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 340呎 (2房)
 招标单位
@@ -16067,7 +16105,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 240呎 (1房)
 $715万
@@ -16075,7 +16113,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 236呎 (1房)
 $565万
@@ -16083,7 +16121,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 233呎 (1房)
 $551万
@@ -16091,7 +16129,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 232呎 (1房)
 $559万
@@ -16099,7 +16137,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>G | 232呎 (1房)
 $554万
@@ -16107,7 +16145,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="18" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (1房)
 $545万
@@ -16115,7 +16153,7 @@
 (23年-07月)</t>
         </is>
       </c>
-      <c r="J27" s="18" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>J | 238呎 (1房)
 $615万
@@ -16123,7 +16161,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K27" s="18" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>K | 336呎 (1房)
 $666万
@@ -16131,7 +16169,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="L27" s="18" t="inlineStr">
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>L | 193呎 (开放式)
 $388万
@@ -16139,7 +16177,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="M27" s="18" t="inlineStr">
+      <c r="M26" s="22" t="inlineStr">
         <is>
           <t>M | 193呎 (开放式)
 $392万
@@ -16147,7 +16185,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="N27" s="18" t="inlineStr">
+      <c r="N26" s="22" t="inlineStr">
         <is>
           <t>N | 286呎 (1房)
 $602万
@@ -16158,7 +16196,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
